--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ARIZONA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ARIZONA_2020.xlsx
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C93">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C118">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C120">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C182">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C241">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C249">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C258">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C340">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C379">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C605">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C618">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C634">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C654">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C884">
